--- a/data/trans_camb/P1402-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1402-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,7</t>
+          <t>6,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>6,78</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 8,89</t>
+          <t>2,58; 9,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,44</t>
+          <t>4,51; 11,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 11,19</t>
+          <t>3,78; 10,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,76</t>
+          <t>1,02; 6,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,82</t>
+          <t>2,24; 8,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,57</t>
+          <t>3,63; 9,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,97</t>
+          <t>2,72; 6,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,98</t>
+          <t>4,17; 8,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,46</t>
+          <t>4,29; 8,88</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,52; 85,17</t>
+          <t>19,7; 87,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,84; 108,37</t>
+          <t>33,8; 107,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,48; 105,88</t>
+          <t>29,07; 99,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 51,95</t>
+          <t>5,83; 52,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,04; 68,47</t>
+          <t>14,27; 67,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,18; 75,62</t>
+          <t>23,45; 73,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,65; 56,72</t>
+          <t>19,25; 55,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,69; 72,83</t>
+          <t>28,99; 72,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,07; 78,78</t>
+          <t>29,85; 71,64</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>3,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,03</t>
+          <t>-0,31; 2,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,42</t>
+          <t>1,65; 4,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,38</t>
+          <t>3,3; 5,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,14</t>
+          <t>-0,11; 2,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,39</t>
+          <t>1,01; 3,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,89</t>
+          <t>1,5; 3,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,79</t>
+          <t>0,19; 1,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,55</t>
+          <t>1,71; 3,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,83</t>
+          <t>2,62; 4,33</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127,82%</t>
+          <t>155,02%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>119,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>111,35%</t>
+          <t>139,89%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 84,04</t>
+          <t>-9,64; 81,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,19; 179,15</t>
+          <t>45,24; 171,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,76; 223,75</t>
+          <t>88,82; 249,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 134,84</t>
+          <t>-4,82; 139,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,97; 223,34</t>
+          <t>37,97; 227,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,65; 174,15</t>
+          <t>55,48; 229,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 81,73</t>
+          <t>3,79; 79,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,39; 161,52</t>
+          <t>57,91; 159,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,89; 177,62</t>
+          <t>85,14; 199,7</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>2,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,71</t>
+          <t>-1,41; 2,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,83</t>
+          <t>-0,03; 4,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,79</t>
+          <t>2,46; 7,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,61</t>
+          <t>-1,99; 1,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,82</t>
+          <t>-0,97; 2,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,32</t>
+          <t>-0,78; 2,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,36</t>
+          <t>-1,18; 1,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,99</t>
+          <t>-0,0; 2,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,95</t>
+          <t>1,52; 4,32</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192,03%</t>
+          <t>204,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>128,25%</t>
+          <t>138,82%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,32; 184,45</t>
+          <t>-51,46; 177,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 311,73</t>
+          <t>-7,04; 342,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,47; 450,6</t>
+          <t>62,52; 490,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-74,66; 193,2</t>
+          <t>-75,11; 164,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,89; 348,53</t>
+          <t>-41,57; 253,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 283,71</t>
+          <t>-27,06; 277,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,05; 86,67</t>
+          <t>-49,4; 115,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 210,47</t>
+          <t>-0,85; 210,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,31; 278,6</t>
+          <t>51,88; 334,38</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>2,32</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,15</t>
+          <t>0,57; 2,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,36</t>
+          <t>1,84; 4,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,41</t>
+          <t>2,42; 4,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,1</t>
+          <t>0,62; 3,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,97</t>
+          <t>0,4; 2,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,58</t>
+          <t>-0,03; 2,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,74</t>
+          <t>0,91; 2,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,24</t>
+          <t>1,55; 3,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,69</t>
+          <t>1,5; 3,07</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,97; 63,13</t>
+          <t>9,49; 57,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,39; 87,71</t>
+          <t>29,48; 84,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,84; 84,98</t>
+          <t>38,8; 94,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,48; 50,7</t>
+          <t>8,35; 50,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 47,68</t>
+          <t>5,32; 49,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 25,7</t>
+          <t>-0,31; 34,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,11; 46,6</t>
+          <t>13,55; 45,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,27; 56,25</t>
+          <t>23,2; 56,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,24; 45,41</t>
+          <t>22,4; 53,11</t>
         </is>
       </c>
     </row>
